--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E519"/>
+  <dimension ref="A1:E539"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14436,6 +14436,466 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>TestContextManagerRealTokens</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>真实token覆盖估算</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>提供last_prompt_tokens时使用真实值而非estimate_tokens</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>TestContextManagerRealTokens</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>无真实token回退估算</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>last_prompt_tokens=None时回退到estimate_tokens()</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>TestContextManagerRealTokens</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>None与不传参数等价</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>last_prompt_tokens=None与不传参数行为一致</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>TestContextManagerRealTokens</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>真实token阻止误压缩</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>估算显示超限但真实token显示安全时不压缩</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>TestContextManagerRealTokens</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>verbose输出来源标记</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>verbose模式下输出[real]或[estimated]标记</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>TestCompressorRealTokens</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>should_compress使用真实token</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>提供last_prompt_tokens时直接与threshold比较</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>TestCompressorRealTokens</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>should_compress回退估算</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>last_prompt_tokens=None时使用estimate_tokens</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>TestCompressorRealTokens</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>compress透传last_prompt_tokens</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>compress()将last_prompt_tokens传递给should_compress()</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>TestCompressorRealTokens</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>真实token低于阈值不压缩</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>real tokens &lt; threshold时compress返回原消息列表</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>TestCompressorRealTokens</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>禁用压缩器忽略真实token</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>enabled=False时无论真实token多高都不压缩</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>TestReActAgentRealTokenIntegration</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>初始状态为None</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>_last_prompt_tokens初始化为None</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>TestReActAgentRealTokenIntegration</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>LLM调用后存储真实token</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>usage.prompt_tokens&gt;0时更新_last_prompt_tokens</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>TestReActAgentRealTokenIntegration</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>_prepare_run重置token</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>_prepare_run()将_last_prompt_tokens重置为None</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>TestReActAgentRealTokenIntegration</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>check_and_compress接收真实token</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>_think()传递_last_prompt_tokens给check_and_compress</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>TestReActAgentRealTokenIntegration</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>should_compress接收真实token</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>_think()传递_last_prompt_tokens给should_compress</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>TestReActAgentRealTokenIntegration</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>compress接收真实token</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>_think()传递_last_prompt_tokens给compress</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>TestBackwardCompatibility</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>check_and_compress无需新参数</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>不传last_prompt_tokens时check_and_compress正常工作</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>TestBackwardCompatibility</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>should_compress无需新参数</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>不传last_prompt_tokens时should_compress正常工作</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>TestBackwardCompatibility</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>compress无需新参数</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>不传last_prompt_tokens时compress正常工作</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>决策点真实Token</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>TestBackwardCompatibility</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>estimate_tokens仍可用</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>estimate_tokens()作为回退仍可正常调用</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E539"/>
+  <dimension ref="A1:E580"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14457,7 +14457,6 @@
           <t>提供last_prompt_tokens时使用真实值而非estimate_tokens</t>
         </is>
       </c>
-      <c r="E520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -14480,7 +14479,6 @@
           <t>last_prompt_tokens=None时回退到estimate_tokens()</t>
         </is>
       </c>
-      <c r="E521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -14503,7 +14501,6 @@
           <t>last_prompt_tokens=None与不传参数行为一致</t>
         </is>
       </c>
-      <c r="E522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -14526,7 +14523,6 @@
           <t>估算显示超限但真实token显示安全时不压缩</t>
         </is>
       </c>
-      <c r="E523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -14549,7 +14545,6 @@
           <t>verbose模式下输出[real]或[estimated]标记</t>
         </is>
       </c>
-      <c r="E524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -14572,7 +14567,6 @@
           <t>提供last_prompt_tokens时直接与threshold比较</t>
         </is>
       </c>
-      <c r="E525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -14595,7 +14589,6 @@
           <t>last_prompt_tokens=None时使用estimate_tokens</t>
         </is>
       </c>
-      <c r="E526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -14618,7 +14611,6 @@
           <t>compress()将last_prompt_tokens传递给should_compress()</t>
         </is>
       </c>
-      <c r="E527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -14641,7 +14633,6 @@
           <t>real tokens &lt; threshold时compress返回原消息列表</t>
         </is>
       </c>
-      <c r="E528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -14664,7 +14655,6 @@
           <t>enabled=False时无论真实token多高都不压缩</t>
         </is>
       </c>
-      <c r="E529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -14687,7 +14677,6 @@
           <t>_last_prompt_tokens初始化为None</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -14710,7 +14699,6 @@
           <t>usage.prompt_tokens&gt;0时更新_last_prompt_tokens</t>
         </is>
       </c>
-      <c r="E531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -14733,7 +14721,6 @@
           <t>_prepare_run()将_last_prompt_tokens重置为None</t>
         </is>
       </c>
-      <c r="E532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -14756,7 +14743,6 @@
           <t>_think()传递_last_prompt_tokens给check_and_compress</t>
         </is>
       </c>
-      <c r="E533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -14779,7 +14765,6 @@
           <t>_think()传递_last_prompt_tokens给should_compress</t>
         </is>
       </c>
-      <c r="E534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -14802,7 +14787,6 @@
           <t>_think()传递_last_prompt_tokens给compress</t>
         </is>
       </c>
-      <c r="E535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -14825,7 +14809,6 @@
           <t>不传last_prompt_tokens时check_and_compress正常工作</t>
         </is>
       </c>
-      <c r="E536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -14848,7 +14831,6 @@
           <t>不传last_prompt_tokens时should_compress正常工作</t>
         </is>
       </c>
-      <c r="E537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -14871,7 +14853,6 @@
           <t>不传last_prompt_tokens时compress正常工作</t>
         </is>
       </c>
-      <c r="E538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -14894,7 +14875,908 @@
           <t>estimate_tokens()作为回退仍可正常调用</t>
         </is>
       </c>
-      <c r="E539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxChars</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>纯英文截断</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>英文文本 calculate_max_chars 正确反算字符数</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxChars</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>纯中文截断</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>中文文本 calculate_max_chars 正确反算字符数</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxChars</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>中英混合截断</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>混合文本 calculate_max_chars 正确反算字符数</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxChars</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>短文本无需截断</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>文本在预算内时返回全文长度</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxChars</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>空文本</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>空文本返回0</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxChars</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>零预算</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>零token预算返回0</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxChars</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>负预算</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>负token预算返回0</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxChars</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>二分查找收敛</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>截断后估算token数 &lt;= max_tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxChars</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>单token预算</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>极小预算仍能找到有效字符数</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxChars</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>精确匹配</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>文本恰好等于预算时返回全文长度</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>TestEstimateTokensWithCalibration</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>默认校准为1</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>calibration_factor=1.0 时结果与无校准相同</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>TestEstimateTokensWithCalibration</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>校准系数1.5</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>calibration_factor=1.5 估算值增大</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>TestEstimateTokensWithCalibration</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>校准系数0.8</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>calibration_factor=0.8 估算值减小</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>TestEstimateTokensWithCalibration</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>消息列表校准</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>estimate_tokens() 消息列表也支持校准</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>TestResultSummarizerEstimateTokens</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>统一估算支持中文</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>result_summarizer.estimate_tokens 支持中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>TestResultSummarizerEstimateTokens</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>与token_utils一致</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>result_summarizer 估算与 token_utils 结果一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>TestMaxSummaryTokensActivation</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>超预算截断</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>摘要超过 max_summary_tokens 时截断</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>TestMaxSummaryTokensActivation</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>未预算不截断</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>摘要未超过 max_summary_tokens 时保持完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>TestMaxSummaryTokensActivation</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>零预算不截断</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>max_summary_tokens=0 时不截断</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>截断比率</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>TestCompressorTruncation</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>中文摘要截断</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>压缩器中文摘要使用 calculate_max_chars 截断</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>TestCalibrationData</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>创建数据点</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>CalibrationData 存储 estimated 和 actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>TestCalibrationData</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>相等比较</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>CalibrationData 支持相等比较</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>TestRecordCalibrationData</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>记录数据点</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>record_calibration_data 添加条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>TestRecordCalibrationData</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>窗口大小限制</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>超过 calibration_window 时裁剪旧数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>TestRecordCalibrationData</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>禁用时不记录</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>calibration_enabled=False 时不记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>TestRecordCalibrationData</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>触发更新</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>记录数据后触发 _update_calibration</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>TestCalibrationUpdate</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>低估系数&gt;1</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>actual&gt;estimated 时校准系数 &gt; 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>TestCalibrationUpdate</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>高估系数&lt;1</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>actual&lt;estimated 时校准系数 &lt; 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>TestCalibrationUpdate</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>准确系数≈1</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>actual≈estimated 时校准系数 ≈ 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>TestCalibrationUpdate</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>下限clamp</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>极低比例 clamp 到 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>TestCalibrationUpdate</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>上限clamp</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>极高比例 clamp 到 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>TestCalibrationUpdate</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>最少采样</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>&lt;3 个样本时不更新校准</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>TestCalibrationUpdate</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>禁用不更新</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>calibration_enabled=False 时不更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>TestCalibrationUpdate</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>除零保护</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>estimated=0 时 max(estimated,1) 防止除零</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>TestCalibrationConsumedByEstimate</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>估算增大</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>calibration_factor&gt;1 时 estimate_tokens 增大</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>TestCalibrationConsumedByEstimate</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>文本估算减小</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>calibration_factor&lt;1 时 estimate_text_tokens 减小</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>TestCalibrationConsumedByEstimate</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>校准改变决策</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>不同校准系数改变压缩决策</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>TestCalibrationIntegration</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>多轮收敛</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>多次调用后校准系数收敛</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>TestCalibrationIntegration</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>重置清除</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>reset() 清除校准数据和系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>TestCalibrationIntegration</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>状态包含样本数</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>get_status() 包含 calibration_samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>校准闭环</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>TestCalibrationIntegration</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>影响上下文决策</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>校准系数影响 check_and_compress 决策</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E580"/>
+  <dimension ref="A1:E612"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15778,6 +15778,735 @@
         </is>
       </c>
     </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentResult</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>SIMPLE结果</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>验证 PrejudgmentResult SIMPLE 分类和答案</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentResult</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>COMPLEX结果无答案</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>验证 COMPLEX 结果 answer=None</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentResult</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>MODERATE结果无答案</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>验证 MODERATE 结果 answer=None</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentParsing</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>解析simple标记</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>解析 [COMPLEXITY: simple] + 答案文本</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>标记格式不符导致解析失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentParsing</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>解析moderate标记</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>解析 [COMPLEXITY: moderate] 无答案</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentParsing</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>解析complex标记</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>解析 [COMPLEXITY: complex] 无答案</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentParsing</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>大小写不敏感</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>[Complexity: Simple] 也能正确解析</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentParsing</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>无标记默认COMPLEX</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>无标记响应默认返回 COMPLEX</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>解析失败导致误判为 SIMPLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentParsing</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>无效标记默认COMPLEX</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>[COMPLEXITY: unknown] 默认返回 COMPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentParsing</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>SIMPLE多行答案提取</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>标记后多行文本作为答案提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentParsing</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>标记在中间位置</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>标记出现在响应中间也能正确提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentParsing</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>SIMPLE空答案</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>[COMPLEXITY: simple] 无后续文本时 answer=None</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentWithMockLLM</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>预判SIMPLE</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Mock LLM 返回 SIMPLE 分类和答案</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>LLM 返回格式异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentWithMockLLM</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>预判MODERATE</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Mock LLM 返回 MODERATE 分类</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentWithMockLLM</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>预判COMPLEX</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Mock LLM 返回 COMPLEX 分类</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentWithMockLLM</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>无标记默认COMPLEX</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>LLM 无标记响应默认 COMPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentWithMockLLM</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>LLM异常默认COMPLEX</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>LLM 调用异常时安全回退 COMPLEX</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>异常未捕获导致崩溃</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentWithMockLLM</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>LLM不可用默认COMPLEX</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>llm=None 时返回 COMPLEX 回退</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentWithMockLLM</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>极简消息列表</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>LLM 调用使用 tools=None 和 system_stable=None</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>TestQueryPrejudgmentWithMockLLM</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>事实性问题分类</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>GIL 问题被分类为 SIMPLE 并生成答案</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentRouterIntegration</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Router SIMPLE不触发预判</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>QueryRouter SIMPLE 分类不触发 LLM 预判</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentRouterIntegration</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Router MODERATE不触发预判</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>QueryRouter MODERATE 分类不触发 LLM 预判</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentRouterIntegration</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Router默认COMPLEX触发预判</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>默认 COMPLEX（reason含defaulting）触发预判</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>should_prejudge 逻辑错误导致不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentRouterIntegration</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Router匹配COMPLEX不触发预判</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>正则匹配的 COMPLEX 不触发预判</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentRouterIntegration</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>should_prejudge逻辑</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>验证三种场景的预判触发判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentConfig</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>默认禁用</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>prejudgment_enabled 默认 False</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentConfig</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>默认空提示词</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>prejudgment_simple_prompt 默认空字符串</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentConfig</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>默认max_answer_tokens</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>prejudgment_max_answer_tokens 默认 300</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentConfig</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>自定义值</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>自定义 enabled/prompt/max_answer_tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentConfig</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>配置解析</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>ConfigLoader 解析 prejudgment YAML 字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentConfig</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>配置默认值</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>ConfigLoader 空 dict 时的默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>预判机制</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>TestPrejudgmentConfig</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>配置保存往返</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>save/load 往返保留所有 prejudgment 字段</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E612"/>
+  <dimension ref="A1:E652"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16507,6 +16507,886 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>TestRoutingResultBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>默认预算比例1.0</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>RoutingResult 默认 suggested_budget_ratio=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>TestRoutingResultBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>自定义预算比例</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>RoutingResult 设置 suggested_budget_ratio=0.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>TestQueryRouterBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>SIMPLE查询小预算</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>你好 → SIMPLE, budget_ratio=0.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>TestQueryRouterBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>MODERATE查询中预算</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>读取 config.yaml → MODERATE, budget_ratio=0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>TestQueryRouterBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>COMPLEX查询全预算</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>分析代码 → COMPLEX, budget_ratio=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>TestQueryRouterBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>禁用路由返回全预算</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>routing disabled → COMPLEX, budget_ratio=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>TestQueryRouterBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>默认复杂返回全预算</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>无匹配 → COMPLEX, budget_ratio=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>TestQueryRouterBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>自定义预算比例配置</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>simple=0.1, moderate=0.3, complex=0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>TestTokenBudgetSetBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>比例调整初始预算</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>set_budget_ratio(0.15, 100000) → initial=15000</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>TestTokenBudgetSetBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>比例重置已消耗</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>消耗50000后 set_budget_ratio 重置 consumed=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>TestTokenBudgetSetBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>比例重置警告状态</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>set_budget_ratio 重置 warning_level/warnings_issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>TestTokenBudgetSetBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>最小比例5%底线</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>set_budget_ratio(0.01) → clamp到5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>TestTokenBudgetSetBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>全比例1.0</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>set_budget_ratio(1.0) → initial 不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>TestTokenBudgetSetBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>中等比例0.5</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>set_budget_ratio(0.5, 50000) → initial=25000</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>TestTokenBudgetSetBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>比例影响警告阈值</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>调整后 remaining/initial 比例正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>复杂度预算</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>TestTokenBudgetSetBudgetRatio</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>不同基础预算</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>base=120000, ratio=0.5 → initial=60000</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>TestStallConfig</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>默认配置</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>enabled=True, patience=3, threshold=0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>TestStallConfig</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>自定义配置</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>enabled=False, patience=5, threshold=0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>TestStallResult</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>未停滞结果</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>is_stalled=False, hint=None</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>TestStallResult</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>停滞结果带提示</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>is_stalled=True, hint=非空</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>TestStallDetectorBasic</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>首次迭代不检测</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>1次迭代 → not stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>TestStallDetectorBasic</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>不同迭代不停滞</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>不同工具/结果 → not stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>TestStallDetectorBasic</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>相同迭代检测停滞</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>2次相同 → stalled (patience=2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>TestStallDetectorBasic</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>patience=3检测</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>3次相同 → stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>TestStallDetectorBasic</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>patience未达到前</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>2次相同 patience=3 → 检查已有数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>TestStallDetectorSimilarity</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>不同工具不停滞</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>file_read vs shell_execute → not stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>TestStallDetectorSimilarity</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>同工具不同结果不停滞</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>file_read 不同结果 → not stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>TestStallDetectorSimilarity</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>同工具同结果停滞</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>file_read 相同结果 → stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>TestStallDetectorSimilarity</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>混合工具部分相似</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>3次完全相同混合调用 → stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>TestStallDetectorHints</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>停滞时生成提示</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>stalled + hint_injection=True → hint 非空</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>TestStallDetectorHints</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>禁用提示不生成</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>stalled + hint_injection=False → hint=None</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>TestStallDetectorHints</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>提示循环变体</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>连续stall 产生不同提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>TestStallDetectorReset</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>重置清除状态</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>reset后 check_stall → not stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>TestStallDetectorReset</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>重置后重新检测</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>reset后新迭代 → 正常检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>TestStallDetectorDisabled</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>禁用从不检测</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>enabled=False + 10次相同 → not stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>TestStallDetectorEdgeCases</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>空工具调用</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>空调用2次 → stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>TestStallDetectorEdgeCases</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>长结果</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>10000字符结果 → stalled</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>TestStallDetectorEdgeCases</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>停滞计数递增</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>连续stall → stalled_iterations 递增</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>TestStallDetectorEdgeCases</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>进展重置计数</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>不同迭代 → stall_count=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Stall Detection</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>TestStallDetectorEdgeCases</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Unicode结果</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>中文内容 → 正确检测</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E652"/>
+  <dimension ref="A1:E684"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17387,6 +17387,710 @@
         </is>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>TestToolOffloadConfig</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>默认配置</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>enabled=True, size_threshold=1000, auto_cleanup=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>TestToolOffloadConfig</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>自定义配置</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>自定义 enabled/size_threshold/offload_dir</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>禁用时不卸载</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>enabled=False → should_offload=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>工具不支持不卸载</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>can_offload=False → should_offload=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>低于阈值不卸载</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>小内容 → should_offload=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>超过阈值触发卸载</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>大内容+can_offload → should_offload=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>排除工具不卸载</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>memorize → should_offload=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>卸载写文件</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>offload() → 临时文件存在且内容正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>卸载返回摘要</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>摘要包含 [结果已卸载] 和 file_read 路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>卸载跟踪元数据</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>original_size_tokens &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>cleanup清理文件</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>cleanup() → 临时文件删除</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>统计信息</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>get_stats() → offloaded_count, total_tokens_saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>按ID查询</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>get_offloaded() → 正确结果且 accessed=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>TestToolOffloadManager</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>按路径查询</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>get_by_path() → 正确结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>TestBaseToolCanOffload</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>默认can_offload</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>BaseTool.can_offload=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Tool Offload</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>TestBaseToolCanOffload</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>设置can_offload</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>can_offload=True 生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>TestCacheConfigExtended</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>默认多轮字段</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>persist=False, warmup_on_restore=True, mtime_invalidation=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>TestCacheConfigExtended</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>自定义多轮字段</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>自定义 persist/persist_dir/warmup_on_restore</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>TestCacheMtimeInvalidation</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>mtime变化失效</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>文件修改后缓存失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>TestCacheMtimeInvalidation</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>mtime不变有效</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>文件未修改缓存有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>TestCacheMtimeInvalidation</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>非文件工具无mtime检查</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>shell_execute 不受 mtime 影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>TestCacheMtimeInvalidation</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>自动提取文件路径</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>从 args 自动提取 file_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>TestCacheMtimeInvalidation</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>禁用mtime检查</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>mtime_invalidation=False → 文件修改不影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>TestCachePersistence</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>持久化到磁盘</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>persist_to_disk() → manifest.json 存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>TestCachePersistence</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>从磁盘预热</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>warmup_from_disk() → 加载缓存</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>TestCachePersistence</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>跳过过期条目</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>过期条目不加载</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>TestCachePersistence</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>跳过过期文件</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>mtime 变化的条目不加载</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>TestCachePersistence</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>空manifest</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>不存在的目录 → 返回 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>TestCacheOffloadIntegration</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>缓存存储卸载摘要</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>is_offloaded=True 时缓存摘要</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>TestCacheOffloadIntegration</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>统计跟踪卸载条目</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>offloaded_entries 计数正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>TestCacheEntry</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>offload标志</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>is_offloaded=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Multi-turn Cache</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>TestCacheEntry</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>文件mtime</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>file_mtimes 正确记录</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E684"/>
+  <dimension ref="A1:E722"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18091,6 +18091,842 @@
         </is>
       </c>
     </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditConfig</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>默认值</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>enabled=True, threshold=0.50, window=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditConfig</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>自定义值</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>自定义配置项正确设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditRecord</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>基本记录</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>deviation_pct=0.20, direction=under</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditRecord</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>高估</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>estimated&gt;actual, direction=over</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditRecord</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>低估</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>estimated&lt;actual, direction=under</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditRecord</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>零估算</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>estimated=0 返回 unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditRecord</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>禁用状态</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>enabled=False 返回零偏差</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditRecord</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>窗口裁剪</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>超过 audit_window 保留最近 N 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditWarning</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>低于阈值</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>40% 偏差不告警</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditWarning</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>等于阈值</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>50% 偏差不告警（NOT &gt;）</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditWarning</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>超过阈值</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>60% 偏差触发 WARNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditWarning</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>自定义阈值</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>30% 阈值下 40% 触发告警</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditWarning</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>告警计数</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>warning_count 正确跟踪</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditConvergence</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>&lt;5 样本不收敛</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditConvergence</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>已收敛</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>5 个 &lt;10% 偏差判定收敛</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditConvergence</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>未收敛</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>1 个高偏差打破收敛</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditConvergence</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>自定义阈值</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>3 样本 + 5% 阈值收敛</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditSummary</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>空摘要</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>total_checks=0, avg=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditSummary</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>有数据摘要</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>avg/max/over/under 统计正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>TestEstimationAuditSummary</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>校准因子</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>calibration_factor 在摘要中</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>TestPromptModuleEffectiveEstimate</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>动态估算</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>纯文本用 estimate_text_tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>TestPromptModuleEffectiveEstimate</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>模板回退</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>含 {tools_description} 回退硬编码</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>TestPromptModuleEffectiveEstimate</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>空内容回退</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>空 content 回退 token_estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>TestPromptModuleEffectiveEstimate</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>动态匹配</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>与 estimate_text_tokens 结果一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>TestResultSummarizerCalibration</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>校准截断</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>calibration_factor 影响截断长度</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>TestResultSummarizerCalibration</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>校准估算</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>calibration_factor=1.5 &gt;= 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxCharsCalibration</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>校准字符数</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>calibration_factor 越大字符数越少</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxCharsCalibration</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>空文本</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>返回 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>TestCalculateMaxCharsCalibration</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>零 max_tokens</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>返回 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>TestBaseRatioFirstRoundCorrection</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>tracker 有审计属性</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>estimation_audit + get_estimation_audit_summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>TestBaseRatioFirstRoundCorrection</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>base_ratio 修正字段</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>_base_ratio_initialized + _base_ratio_iteration</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>TestSmartOptimizationConfigCalibration</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>默认值</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>calibration_enabled=True, audit_enabled=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>TestSmartOptimizationConfigCalibration</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>自定义值</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>自定义校准/审计配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>TestLLMCallMetricsNewFields</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>默认值</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>estimated_tokens=0, deviation_pct=0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>TestLLMCallMetricsNewFields</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>自定义值</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>新字段正确设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>TestLLMCallMetricsNewFields</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>to_dict 序列化</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>新字段包含在字典中</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>TestRawLLMCallDataNewFields</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>默认值</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>estimated_tokens=0, calibration_factor=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>TestRawLLMCallDataNewFields</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>自定义值</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>新字段正确设置</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E722"/>
+  <dimension ref="A1:E728"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18927,6 +18927,138 @@
         </is>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>TestBaseRatioFirstRoundCorrection</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>单轮迭代不设 base_ratio</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>单轮迭代 run 不设置 base_ratio，使用 per-iteration ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>TestBaseRatioFirstRoundCorrection</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>两轮迭代从第二轮设 base_ratio</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>两轮迭代 run 从第二轮设置 base_ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>TestBaseRatioFirstRoundCorrection</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>三轮迭代 base_ratio 稳定</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>三轮迭代 base_ratio 从第二轮设置，第三轮保持一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>TestBaseRatioFirstRoundCorrection</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>跨 run 重置 base_ratio</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>start_run() 重置 base_ratio 相关字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>TestBaseRatioFirstRoundCorrection</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>首轮 breakdown 准确</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>首轮使用 per-iteration ratio，token 分类之和等于 prompt_tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Estimation Audit</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>TestBaseRatioFirstRoundCorrection</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>message_tokens 不为负</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>max(0,...) 守卫确保 message_tokens &gt;= 0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E728"/>
+  <dimension ref="A1:E762"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19059,6 +19059,754 @@
         </is>
       </c>
     </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Embedding</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>TestEmbeddingConfig</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>默认配置</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>provider=ollama, model=nomic-embed-text, timeout=30</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Embedding</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>TestEmbeddingConfig</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>自定义配置</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>provider=openai, model=text-embedding-3-small, api_key=sk-test</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Embedding</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>TestOllamaEmbeddingClient</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>单文本嵌入</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>调用 /api/embed 端点，返回 embedding 向量</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Embedding</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>TestOllamaEmbeddingClient</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>批量嵌入</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>embed_batch 返回多个向量</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Embedding</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>TestOllamaEmbeddingClient</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>HTTP 错误处理</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>服务不可用时 raise_for_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Embedding</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>TestOllamaEmbeddingClient</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>base_url 尾部斜杠</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>自动去除尾部 /</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Embedding</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>TestCreateEmbeddingClient</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>ollama 客户端</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>provider=ollama 创建 OllamaEmbeddingClient</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Embedding</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>TestCreateEmbeddingClient</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>sentence_transformers 客户端</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>provider=sentence_transformers 创建对应客户端</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Embedding</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>TestCreateEmbeddingClient</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>openai 客户端</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>provider=openai 创建 OpenAIEmbeddingClient</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Embedding</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>TestCreateEmbeddingClient</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>不支持 provider</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>provider=unknown 抛出 ValueError</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>TestCosineSimilarity</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>相同向量</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>余弦相似度 ≈ 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>TestCosineSimilarity</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>正交向量</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>余弦相似度 ≈ 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>TestCosineSimilarity</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>相反向量</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>余弦相似度 ≈ -1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>TestCosineSimilarity</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>零向量</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>返回 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>TestCosineSimilarity</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>空向量</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>返回 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>TestCosineSimilarity</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>不同长度</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>返回 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>TestContentHash</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>相同文本同哈希</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>_content_hash(hello) == _content_hash(hello)</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>TestContentHash</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>不同文本不同哈希</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>_content_hash(hello) != _content_hash(world)</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>TestContentHash</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>返回十六进制字符串</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>结果仅含 0-9a-f 字符</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressorConfig</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>默认配置</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>enabled=False, threshold=0.85, min_messages=8, provider=ollama</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressorConfig</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>自定义配置</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>enabled=True, threshold=0.9, provider=openai</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>禁用不压缩</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>enabled=False 时 should_compress 返回 False</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>消息不足不压缩</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>消息数 &lt; min_messages_to_compress 不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>消息足够触发</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>消息数 &gt;= min_messages_to_compress 触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>合并相似消息</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>相似 embedding 的消息被合并，结果更短</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>不合并不同消息</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>正交 embedding + 高阈值，不合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>不同 role 不合并</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>user 和 assistant 即使 embedding 相似也不合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>embedding 失败降级</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>embed_batch 抛异常时返回原消息，_available=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>统计追踪</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>compression_count 和 messages_merged 正确记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>reset_stats</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>重置后所有统计归零</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>embedding 缓存命中</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>相同内容第二次 embed_batch 调用次数减少</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>system 消息保留</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>system 角色消息不参与合并，保留在结果开头</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>高阈值不合并</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>正交 embedding + 0.9999 阈值不触发合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Semantic Compressor</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>TestSemanticCompressor</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>merge_tag 标注</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>合并后的消息内容包含 merged tag</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E762"/>
+  <dimension ref="A1:E791"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19807,6 +19807,644 @@
         </is>
       </c>
     </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>TestIsRetryableError</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>429 可重试</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>HTTP 429 限流应可重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>TestIsRetryableError</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>500 可重试</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>HTTP 500 服务端错误应可重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>TestIsRetryableError</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>502/503 可重试</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>HTTP 502/503 应可重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>TestIsRetryableError</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>400/401/403/404 不可重试</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>客户端错误不应重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>TestIsRetryableError</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>ConnectionError 可重试</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>网络连接错误应可重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>TestIsRetryableError</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>TimeoutError 可重试</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>超时错误应可重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>TestIsRetryableError</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>ValueError/TypeError 不可重试</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>逻辑错误不应重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>TestIsRetryableError</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>自定义状态码</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>retryable_status_codes 配置可自定义</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>TestIsRetryableError</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>requests 异常</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>requests.exceptions.ConnectionError/Timeout 可重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>TestCalculateDelay</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>指数增长</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>delay = base * 2^attempt</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>TestCalculateDelay</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>max_delay 上限</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>延迟不超过 max_delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>TestCalculateDelay</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>jitter 随机性</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>jitter 使延迟在 [base, 2*base) 范围内随机</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>TestWithRetry</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>首次成功</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>函数首次成功不触发重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>TestWithRetry</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>失败后成功</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>可重试错误后重试成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>TestWithRetry</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>不可重试立即抛出</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>不可重试错误不重试直接抛出</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>TestWithRetry</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>重试耗尽抛出</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>超过 max_retries 后抛出最后异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>TestWithRetry</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>on_retry 回调</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>重试时触发回调含 attempt/delay/error</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>TestWithRetry</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>延迟指数递增</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>sleep 延迟按指数增长</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>TestWithRetry</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>零次重试</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>max_retries=0 不重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>TestWithRetry</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>429 重试成功</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>HTTP 429 重试后成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>TestBaseLLMChatRetry</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>chat 自动重试</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>BaseLLM.chat() 自动重试瞬态错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>TestBaseLLMChatRetry</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>disabled 不重试</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>retry.enabled=False 不重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>TestBaseLLMChatRetry</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>无 config 不重试</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>_retry_config=None 不重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>TestBaseLLMChatRetry</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>回调触发</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>_on_retry_callback 在重试时被调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>TestBaseLLMChatRetry</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>不可重试不重试</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>ValueError 等逻辑错误不重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>TestRetryConfig</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>默认值</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>默认配置合理（enabled=True, max_retries=3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>TestRetryConfig</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Config 集成</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>RetryConfig 可从 Config 访问</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>TestRetryConfig</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>dict 解析</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>从 dict 解析 RetryConfig</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>LLM Retry</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>TestRetryConfig</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>YAML 往返</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>保存和加载 YAML 配置一致</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E791"/>
+  <dimension ref="A1:E821"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20445,6 +20445,666 @@
         </is>
       </c>
     </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerConfig</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>test_default_config</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>默认配置值</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerConfig</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>test_custom_config</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>自定义配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerConfig</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>test_config_from_yaml</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>YAML 加载</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckLLMResponse</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>test_normal_response_no_trigger</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>正常响应不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckLLMResponse</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>test_oversized_response_triggers</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>超大响应触发熔断</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckLLMResponse</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>test_exact_threshold_no_trigger</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>边界值不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckLLMResponse</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>test_disabled_never_triggers</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>禁用时不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckLLMResponse</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>test_custom_threshold</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>自定义阈值</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckLLMResponse</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>test_already_suppressed_no_repeat_trigger</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>已降级不重复触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckDuplicate</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>test_no_duplicate_no_trigger</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>非重复不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckDuplicate</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>test_duplicate_below_threshold_no_trigger</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>低于阈值不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckDuplicate</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>test_duplicate_at_threshold_triggers</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>达到阈值触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckDuplicate</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>test_duplicate_above_threshold_triggers</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>超过阈值触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckDuplicate</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>test_custom_duplicate_threshold</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>自定义重复阈值</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckStall</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>test_no_stall_no_trigger</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>无停滞不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckStall</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>test_stall_below_threshold_no_trigger</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>低于阈值不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckStall</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>test_stall_at_threshold_triggers</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>达到阈值触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckStall</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>test_stall_above_threshold_triggers</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>超过阈值触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerCheckStall</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>test_custom_stall_threshold</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>自定义停滞阈值</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerReset</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>test_reset_after_trigger</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>触发后重置</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerReset</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>test_reset_when_already_auto</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>AUTO 模式重置</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerReset</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>test_trigger_after_reset</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>重置后可再次触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerEvents</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>test_event_emitted_on_trigger</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>触发时发送事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerEvents</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>test_no_event_on_second_trigger</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>二次触发不重复事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerEvents</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>test_no_event_when_disabled</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>禁用时不发送事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerIntegration</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker_config_in_smart_optimization</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>配置在 SmartOptimization 中</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerIntegration</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker_config_in_full_config</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>配置在 Config 中</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerIntegration</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker_config_from_yaml</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>YAML 加载配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerIntegration</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>test_execution_mode_enum</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>ExecutionMode 枚举</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker.py</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>TestCircuitBreakerIntegration</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>test_circuit_breaker_event_enum</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>CIRCUIT_BREAKER 事件</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E821"/>
+  <dimension ref="A1:E855"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21105,6 +21105,788 @@
         </is>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>TestTokenBucketRateLimiter</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>bucket_starts_full</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>新限流器初始令牌数等于 burst</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>TestTokenBucketRateLimiter</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>acquire_decrements_tokens</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>acquire() 扣减 1 个令牌</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>TestTokenBucketRateLimiter</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>refill_over_time</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>令牌按时间速率恢复</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>TestTokenBucketRateLimiter</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>acquire_waits_when_empty</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>令牌为 0 时 acquire 阻塞并返回等待时间</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>TestTokenBucketRateLimiter</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>burst_allows_burst</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>允许 burst 次突发请求</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>TestTokenBucketRateLimiter</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>refill_capped_at_max</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>令牌数不超过 max_tokens</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>TestTokenBucketRateLimiter</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>reset_restores_full_bucket</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>reset() 恢复满桶</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>TestWithRateLimit</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>no_wait_when_tokens_available</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>有令牌时立即执行</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>TestWithRateLimit</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>callback_called_when_waiting</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>限流等待时触发 on_wait 回调</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>TestWithRateLimit</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>callback_not_called_when_no_wait</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>无限流时不触发回调</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>TestWithRateLimit</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>function_return_value_passed_through</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>返回值透传</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>TestRateLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>defaults</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>默认配置值正确</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>TestRateLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>config_in_top_level</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Config.rate_limiter 存在且类型正确</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>TestRateLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>config_from_dict</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>_from_dict 解析 rate_limiter 配置</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>TestRateLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>config_save_and_load</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>YAML 往返序列化</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>TestBaseLLMChatRateLimiter</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>chat_with_rate_limit_enabled</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>enabled 时 chat() 走限流路径</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>TestBaseLLMChatRateLimiter</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>chat_without_rate_limit_when_disabled</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>disabled 时跳过限流</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>TestBaseLLMChatRateLimiter</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>chat_without_rate_limit_when_no_config</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>config 为 None 时跳过限流</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>TestBaseLLMChatRateLimiter</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>rate_limit_and_retry_together</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>限流器包裹重试，两层同时生效</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>TestBaseLLMChatRateLimiter</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>on_rate_limit_callback_invoked</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>限流时 _on_rate_limit_callback 被调用</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>TestRateLimiterConfigValidation</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>reject_zero_rpm</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>requests_per_minute=0 抛 ValueError</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>TestRateLimiterConfigValidation</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>reject_negative_rpm</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>requests_per_minute&lt;0 抛 ValueError</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>TestRateLimiterConfigValidation</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>reject_zero_burst</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>burst=0 抛 ValueError</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>TestRateLimiterConfigValidation</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>reject_negative_burst</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>burst&lt;0 抛 ValueError</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>TestRateLimiterConfigValidation</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>valid_config_passes</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>合法配置不抛异常</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>TestBuilderRateLimiterInjection</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>builder_injects_rate_limiter_config</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Builder 注入 rate_limiter_config 和 limiter 实例</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>TestBuilderRateLimiterInjection</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>builder_wires_rate_limit_callback</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>enabled 时连接回调</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>TestBuilderRateLimiterInjection</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>builder_no_callback_when_disabled</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>disabled 时不连接回调</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>TestBuilderRateLimiterInjection</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>rate_limited_event_emitted</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>限流时发射 LLM_RATE_LIMITED 事件</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>TestBuilderRateLimiterInjection</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>rate_limit_and_retry_both_active</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>限流器+重试两层同时活跃</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>TestApplyRateLimit</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>noop_when_disabled</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>disabled 时 _apply_rate_limit 无操作</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>TestApplyRateLimit</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>noop_when_no_config</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>config 为 None 时无操作</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>TestApplyRateLimit</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>acquires_token_when_enabled</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>enabled 时获取令牌</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>rate_limiter</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>TestApplyRateLimit</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>callback_invoked_when_waiting</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>限流时触发回调</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E855"/>
+  <dimension ref="A1:E902"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21126,7 +21126,6 @@
           <t>新限流器初始令牌数等于 burst</t>
         </is>
       </c>
-      <c r="E822" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -21149,7 +21148,6 @@
           <t>acquire() 扣减 1 个令牌</t>
         </is>
       </c>
-      <c r="E823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -21172,7 +21170,6 @@
           <t>令牌按时间速率恢复</t>
         </is>
       </c>
-      <c r="E824" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -21195,7 +21192,6 @@
           <t>令牌为 0 时 acquire 阻塞并返回等待时间</t>
         </is>
       </c>
-      <c r="E825" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -21218,7 +21214,6 @@
           <t>允许 burst 次突发请求</t>
         </is>
       </c>
-      <c r="E826" t="inlineStr"/>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -21241,7 +21236,6 @@
           <t>令牌数不超过 max_tokens</t>
         </is>
       </c>
-      <c r="E827" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -21264,7 +21258,6 @@
           <t>reset() 恢复满桶</t>
         </is>
       </c>
-      <c r="E828" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -21287,7 +21280,6 @@
           <t>有令牌时立即执行</t>
         </is>
       </c>
-      <c r="E829" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -21310,7 +21302,6 @@
           <t>限流等待时触发 on_wait 回调</t>
         </is>
       </c>
-      <c r="E830" t="inlineStr"/>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -21333,7 +21324,6 @@
           <t>无限流时不触发回调</t>
         </is>
       </c>
-      <c r="E831" t="inlineStr"/>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -21356,7 +21346,6 @@
           <t>返回值透传</t>
         </is>
       </c>
-      <c r="E832" t="inlineStr"/>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -21379,7 +21368,6 @@
           <t>默认配置值正确</t>
         </is>
       </c>
-      <c r="E833" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -21402,7 +21390,6 @@
           <t>Config.rate_limiter 存在且类型正确</t>
         </is>
       </c>
-      <c r="E834" t="inlineStr"/>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -21425,7 +21412,6 @@
           <t>_from_dict 解析 rate_limiter 配置</t>
         </is>
       </c>
-      <c r="E835" t="inlineStr"/>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -21448,7 +21434,6 @@
           <t>YAML 往返序列化</t>
         </is>
       </c>
-      <c r="E836" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -21471,7 +21456,6 @@
           <t>enabled 时 chat() 走限流路径</t>
         </is>
       </c>
-      <c r="E837" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -21494,7 +21478,6 @@
           <t>disabled 时跳过限流</t>
         </is>
       </c>
-      <c r="E838" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -21517,7 +21500,6 @@
           <t>config 为 None 时跳过限流</t>
         </is>
       </c>
-      <c r="E839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -21540,7 +21522,6 @@
           <t>限流器包裹重试，两层同时生效</t>
         </is>
       </c>
-      <c r="E840" t="inlineStr"/>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -21563,7 +21544,6 @@
           <t>限流时 _on_rate_limit_callback 被调用</t>
         </is>
       </c>
-      <c r="E841" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -21586,7 +21566,6 @@
           <t>requests_per_minute=0 抛 ValueError</t>
         </is>
       </c>
-      <c r="E842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -21609,7 +21588,6 @@
           <t>requests_per_minute&lt;0 抛 ValueError</t>
         </is>
       </c>
-      <c r="E843" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -21632,7 +21610,6 @@
           <t>burst=0 抛 ValueError</t>
         </is>
       </c>
-      <c r="E844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -21655,7 +21632,6 @@
           <t>burst&lt;0 抛 ValueError</t>
         </is>
       </c>
-      <c r="E845" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -21678,7 +21654,6 @@
           <t>合法配置不抛异常</t>
         </is>
       </c>
-      <c r="E846" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -21701,7 +21676,6 @@
           <t>Builder 注入 rate_limiter_config 和 limiter 实例</t>
         </is>
       </c>
-      <c r="E847" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -21724,7 +21698,6 @@
           <t>enabled 时连接回调</t>
         </is>
       </c>
-      <c r="E848" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -21747,7 +21720,6 @@
           <t>disabled 时不连接回调</t>
         </is>
       </c>
-      <c r="E849" t="inlineStr"/>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -21770,7 +21742,6 @@
           <t>限流时发射 LLM_RATE_LIMITED 事件</t>
         </is>
       </c>
-      <c r="E850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -21793,7 +21764,6 @@
           <t>限流器+重试两层同时活跃</t>
         </is>
       </c>
-      <c r="E851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -21816,7 +21786,6 @@
           <t>disabled 时 _apply_rate_limit 无操作</t>
         </is>
       </c>
-      <c r="E852" t="inlineStr"/>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -21839,7 +21808,6 @@
           <t>config 为 None 时无操作</t>
         </is>
       </c>
-      <c r="E853" t="inlineStr"/>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -21862,7 +21830,6 @@
           <t>enabled 时获取令牌</t>
         </is>
       </c>
-      <c r="E854" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -21885,7 +21852,1040 @@
           <t>限流时触发回调</t>
         </is>
       </c>
-      <c r="E855" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>TestSanitizerConfig</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>default_config</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>默认配置值正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>TestSanitizerConfig</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>custom_config</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>自定义配置生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>TestSanitizerConfig</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>config_in_full_config</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Config 中包含 sanitizer 字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>TestSanitizerConfig</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>custom_patterns_appended</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>自定义模式追加到默认列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>TestSanitizerConfig</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>config_from_dict</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>_from_dict 反序列化正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>TestSanitizerConfig</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>injection_patterns_default_count</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>默认注入模式数量为 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>TestSanitizerResult</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>result_fields</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>SanitizerResult 字段正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>TestSanitizerResult</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>result_rejected</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>被拒绝结果字段正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>TestSanitizerResult</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>result_with_actions</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>带 actions 的结果正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>TestFormatValidation</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>clean_input_passes</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>干净输入通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>TestFormatValidation</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>null_bytes_rejected</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>null bytes 被拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>TestFormatValidation</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>null_bytes_disabled</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>禁用时不拒绝 null bytes</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>TestFormatValidation</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>control_chars_stripped</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>控制字符被剥离</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>TestFormatValidation</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>tab_newline_preserved</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>tab/newline/CR 保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>TestFormatValidation</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>ansi_escape_stripped</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>ANSI escape 被剥离</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>TestFormatValidation</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>mixed_control_chars</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>混合控制字符处理正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>ignore_previous_instructions_rejected</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>"ignore previous instructions" 被拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>disregard_all_rules_rejected</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>"disregard all rules" 被拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>you_are_now_rejected</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>"You are now" 被拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>dan_jailbreak_rejected</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>DAN/jailbreak 模式被拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>chinese_ignore_instructions_rejected</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>中文"忽略之前的指令"被拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>chinese_role_hijack_rejected</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>中文"你现在是"被拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>case_insensitive_match</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>大小写不敏感匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>injection_embedded_in_longer_text</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>注入嵌入长文本仍被检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>normal_input_not_rejected</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>正常输入不被误判</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>custom_pattern_rejected</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>自定义模式生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>TestInjectionPatterns</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>injection_disabled_all_passes</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>enabled 是 orchestrator 层守卫</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>TestLengthValidation</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>short_input_passes</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>短输入通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>TestLengthValidation</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>exact_max_length_passes</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>恰好最大长度通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>TestLengthValidation</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>over_max_length_truncated</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>超长输入被截断</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>TestLengthValidation</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>over_max_length_rejected</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>超长输入被拒绝(reject模式)</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>TestLengthValidation</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>long_line_truncated</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>单行超长被截断</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>TestLengthValidation</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>max_line_length_zero_unlimited</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>max_line_length=0 不限行长</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>TestLengthValidation</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>truncation_preserves_valid_utf8</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>截断保留有效 UTF-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>TestSanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>orchestrator_rejects_injection</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>orchestrator 拒绝注入输入</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>TestSanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>orchestrator_passes_clean_input</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>orchestrator 放行干净输入</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>TestSanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>sanitizer_disabled_in_orchestrator</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>disabled 时 orchestrator 不拦截</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>TestSanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>sanitizer_event_emitted</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>拒绝时发射 INPUT_REJECTED 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>TestSanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>no_event_on_clean_input</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>干净输入不发射事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>TestSanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>execution_result_on_rejection</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>拒绝时返回正确 ExecutionResult</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>TestSanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>orchestrator_truncates_long_input</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>orchestrator 截断超长输入</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>empty_input_passes</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>空输入通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>whitespace_only_input_passes</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>纯空白输入通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>unicode_input_passes</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>unicode 输入通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>code_input_not_flagged</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>代码输入不被误判</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>multiple_violations_first_wins</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>多违规时第一个检查先拦截</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>injection_after_truncation</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>注入在长度检查之前被拦截</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E902"/>
+  <dimension ref="A1:E934"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22887,6 +22887,710 @@
         </is>
       </c>
     </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerPhone</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>chinese_phone_partial_mask</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>中国手机号 partial 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerPhone</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>chinese_phone_full_mask</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>中国手机号 full 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerPhone</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>multiple_phones</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>多个手机号同时遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerPhone</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>phone_not_in_text</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>无手机号时不遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerIDCard</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>chinese_id_card_partial_mask</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>中国身份证 partial 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerIDCard</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>id_card_with_x</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>身份证末位 X 处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerIDCard</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>id_card_full_mask</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>身份证 full 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerEmail</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>email_partial_mask</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>邮箱 partial 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerEmail</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>email_short_prefix</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>短前缀邮箱遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerEmail</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>email_full_mask</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>邮箱 full 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerAPIKey</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>openai_api_key_partial</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>OpenAI API Key partial 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerAPIKey</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>bearer_token</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Bearer token 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerAPIKey</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>github_pat</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>GitHub PAT 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerAPIKey</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>aws_key</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>AWS Key 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerMixed</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>multiple_pii_types</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>多种 PII 同时遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerMixed</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>selective_pii_types</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>选择性启用 PII 类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerMixed</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>no_pii_in_text</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>无 PII 时不遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerMixed</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>custom_mask_char</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>自定义遮蔽字符</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>TestPIIDesensitizerDisabled</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>pii_disabled_no_masking</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>PII 禁用时不遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>TestPIIConfig</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>default_pii_disabled</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>默认 PII 禁用</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>TestPIIConfig</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>pii_config_fields</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>PII 配置字段正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>TestPIIConfig</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>pii_types_default</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>PII 默认类型列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>TestPIIConfig</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>pii_types_custom</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>自定义 PII 类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>TestPIIConfig</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>config_from_dict_with_pii</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>_from_dict 反序列化 PII 配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>TestPIISanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>pii_masked_before_injection_check</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>PII 在注入检查前遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>TestPIISanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>pii_actions_recorded</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>PII 遮蔽记录到 actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>TestPIISanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>pii_disabled_no_action</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>PII 禁用时无 action</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>TestPIISanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>pii_with_injection_both_detected</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>PII+注入同时存在时注入拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>TestPIISanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>pii_result_matches_populated</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>PII 结果填充 pii_matches</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>TestPIISanitizerIntegration</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>rejected_result_has_empty_pii_matches</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>拒绝结果 pii_matches 为空</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>TestPIIOrchestratorIntegration</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>orchestrator_masks_pii</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>orchestrator 遮蔽 PII</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>sanitizer</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>TestPIIOrchestratorIntegration</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>orchestrator_pii_disabled</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>PII 禁用时 orchestrator 不遮蔽</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E934"/>
+  <dimension ref="A1:E1007"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23591,6 +23591,1612 @@
         </is>
       </c>
     </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>TestOutputGuardConfig</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>default_config</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>默认配置值</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>TestOutputGuardConfig</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>custom_config</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>自定义配置值</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>TestOutputGuardConfig</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>config_in_full_config</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Config 包含 output_guard 字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>TestOutputGuardConfig</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>config_from_dict</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>从字典构建配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>TestOutputGuardConfig</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>custom_patterns</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>自定义模式配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>TestOutputGuardResult</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>result_no_sensitive</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>无敏感数据结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>TestOutputGuardResult</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>result_blocked</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>拦截结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>TestOutputGuardResult</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>result_masked</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>遮蔽结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>TestAPIKeyDetection</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>test_openai_api_key</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>OpenAI API key 检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>TestAPIKeyDetection</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>test_github_token</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>GitHub token 检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>TestAPIKeyDetection</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>test_bearer_token</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Bearer token 检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>TestAPIKeyDetection</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>test_aws_access_key</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>AWS access key 检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>TestAPIKeyDetection</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>test_no_api_key</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>无 API key 场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>TestPasswordDetection</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>test_password_equals</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>password= 赋值检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>TestPasswordDetection</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>test_passwd_equals</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>passwd= 赋值检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>TestPasswordDetection</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>test_pwd_equals</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>pwd= 赋值检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>TestPasswordDetection</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>test_secret_equals</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>secret= 赋值检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>TestPasswordDetection</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>test_password_colon</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>password: 冒号分隔检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>TestPasswordDetection</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>test_case_insensitive</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>大小写不敏感</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>TestPasswordDetection</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>test_no_password</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>无密码场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>TestPrivateKeyDetection</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>test_rsa_private_key</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>RSA 私钥检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>TestPrivateKeyDetection</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>test_dsa_private_key</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>DSA 私钥检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>TestPrivateKeyDetection</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>test_ec_private_key</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>EC 私钥检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>TestPrivateKeyDetection</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>test_openssh_private_key</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>OpenSSH 私钥检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>TestPrivateKeyDetection</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>test_no_private_key</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>公钥不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>TestConnectionStringDetection</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>test_postgres_connection</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>PostgreSQL 连接串检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>TestConnectionStringDetection</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>test_mysql_connection</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>MySQL 连接串检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>TestConnectionStringDetection</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>test_mongodb_connection</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>MongoDB 连接串检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>TestConnectionStringDetection</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>test_redis_connection</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Redis 连接串检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>TestConnectionStringDetection</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>test_no_connection_string</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>HTTP URL 不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>TestPIIReuse</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>test_phone_detection</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>手机号检测（复用 PII）</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>TestPIIReuse</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>test_id_card_detection</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>身份证检测（复用 PII）</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>TestPIIReuse</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>test_email_detection</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>邮箱检测（复用 PII）</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>TestMasking</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>test_partial_mask_api_key</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>API key partial 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>TestMasking</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>test_full_mask_api_key</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>API key full 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>TestMasking</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>test_partial_mask_password</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>密码 partial 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>TestMasking</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>test_private_key_masked_as_redacted</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>私钥 REDACTED 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>TestMasking</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>test_connection_string_password_masked</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>连接串密码遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>TestMasking</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>test_phone_partial_mask</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>手机号 partial 遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>TestBlocking</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>test_block_action</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>block 动作拦截</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>TestBlocking</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>test_block_severity_private_key</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>block_severity 私钥强制拦截</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>TestBlocking</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>test_block_severity_not_triggered_for_mask_type</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>非 block_severity 不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>TestBlocking</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>test_block_emits_event</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>拦截触发事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>TestBlocking</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>test_block_severity_emits_event</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>block_severity 触发事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>TestWarning</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>test_warn_action</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>warn 动作不拦截</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>TestWarning</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>test_warn_no_modification</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>warn 不修改输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>test_orchestrator_masks_output</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>orchestrator 遮蔽输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>test_orchestrator_blocks_output</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>orchestrator 拦截输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>test_orchestrator_no_guard</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>无护栏时正常输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>test_orchestrator_guard_disabled</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>护栏禁用时正常输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>test_orchestrator_clean_output</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>清洁输出无遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>TestSensitiveOutputMiddleware</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>test_middleware_masks_output</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>中间件遮蔽工具输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>TestSensitiveOutputMiddleware</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>test_middleware_no_guard</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>无护栏不处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>TestSensitiveOutputMiddleware</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>test_middleware_guard_disabled</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>护栏禁用不处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>TestSensitiveOutputMiddleware</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>test_middleware_no_sensitive_data</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>无敏感数据不处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>TestSensitiveOutputMiddleware</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>test_middleware_failed_result_skipped</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>失败结果跳过</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>TestSensitiveOutputMiddleware</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>test_middleware_priority</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>中间件优先级</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>TestCustomPatterns</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>test_custom_pattern_matches</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>自定义模式匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>TestCustomPatterns</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>test_custom_pattern_masked</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>自定义模式遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>TestCustomPatterns</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>test_invalid_custom_pattern_ignored</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>无效模式忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>test_empty_input</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>空输入</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>test_no_sensitive_data</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>无敏感数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>test_multiple_types_in_same_output</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>多种类型同时检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>test_overlapping_matches_keeps_longer</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>重叠匹配保留更长</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>test_guard_disabled</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>护栏禁用</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>test_guard_enabled</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>护栏启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>test_scan_tool_output</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>工具输出扫描遮蔽</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>test_scan_tool_output_no_sensitive</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>工具输出无敏感数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>test_unicode_output</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Unicode 输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>TestEdgeCases</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>test_very_long_output</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>超长输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>TestSummarizeSensitiveMatches</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>test_empty_matches</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>空匹配摘要</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>TestSummarizeSensitiveMatches</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>test_single_type</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>单类型摘要</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>output_guard</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>TestSummarizeSensitiveMatches</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>test_multiple_types</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>多类型摘要</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1007"/>
+  <dimension ref="A1:E1077"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25197,6 +25197,1546 @@
         </is>
       </c>
     </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentFilterConfig:</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>test_default_config_disabled</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>test_default_config_disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentFilterConfig:</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>test_default_categories</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>test_default_categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentFilterConfig:</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>test_default_action_is_block</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>test_default_action_is_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentFilterConfig:</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>test_custom_config</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>test_custom_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentFilterConfig:</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>test_config_in_full_config</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>test_config_in_full_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentFilterConfig:</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>test_config_from_dict</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>从字典创建配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentFilterConfig:</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>test_custom_patterns</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>test_custom_patterns</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentFilterConfig:</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>test_category_actions</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>test_category_actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>TestHarmfulFilterResult:</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>test_result_no_harmful</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>test_result_no_harmful</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>TestHarmfulFilterResult:</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>test_result_blocked</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>已拦截结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>TestHarmfulFilterResult:</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>test_result_warned</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>已警告结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>TestHarmfulFilterResult:</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>test_result_replaced</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>test_result_replaced</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>TestViolenceDetection:</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>test_bomb_making_english</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>test_bomb_making_english</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>TestViolenceDetection:</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>test_weapon_making_english</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>test_weapon_making_english</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>TestViolenceDetection:</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>test_bomb_making_chinese</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>test_bomb_making_chinese</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>TestViolenceDetection:</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>test_weapon_chinese</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>test_weapon_chinese</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>TestViolenceDetection:</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>test_no_violence_in_safe_text</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>test_no_violence_in_safe_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>TestHateDetection:</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>test_hate_speech_english</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>test_hate_speech_english</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>TestHateDetection:</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>test_hate_speech_chinese</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>test_hate_speech_chinese</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>TestHateDetection:</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>test_no_hate_in_discussion</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>test_no_hate_in_discussion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>TestDangerousDetection:</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>test_suicide_methods_english</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>test_suicide_methods_english</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>TestDangerousDetection:</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>test_suicide_methods_chinese</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>test_suicide_methods_chinese</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>TestDangerousDetection:</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>test_drug_synthesis_english</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>test_drug_synthesis_english</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>TestDangerousDetection:</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>test_hacking_instructions_english</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>test_hacking_instructions_english</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>TestDangerousDetection:</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>test_no_dangerous_in_safe_text</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>test_no_dangerous_in_safe_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>TestIllegalDetection:</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>test_money_laundering_english</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>test_money_laundering_english</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>TestIllegalDetection:</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>test_forgery_instructions_english</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>test_forgery_instructions_english</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>TestIllegalDetection:</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>test_money_laundering_chinese</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>test_money_laundering_chinese</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>TestIllegalDetection:</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>test_no_illegal_in_safe_text</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>test_no_illegal_in_safe_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>TestBlocking:</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>test_block_action_blocks_response</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>test_block_action_blocks_response</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>TestBlocking:</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>test_block_emits_events</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>test_block_emits_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>TestBlocking:</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>test_blocked_response_is_empty</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>test_blocked_response_is_empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>TestBlocking:</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>test_block_reason_includes_categories</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>test_block_reason_includes_categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>TestWarning:</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>test_warn_action_does_not_block</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>test_warn_action_does_not_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>TestWarning:</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>test_warn_prepend_notice</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>test_warn_prepend_notice</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>TestWarning:</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>test_warn_does_not_remove_text</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>test_warn_does_not_remove_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>TestReplacement:</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>test_replace_action_substitutes_text</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>test_replace_action_substitutes_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>TestReplacement:</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>test_custom_replacement_text</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>test_custom_replacement_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>TestReplacement:</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>test_multiple_replacements</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>test_multiple_replacements</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>TestCategoryActions:</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>test_different_actions_per_category</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>test_different_actions_per_category</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>TestCategoryActions:</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>test_category_action_overrides_default</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>test_category_action_overrides_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>TestCategoryActions:</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>test_mixed_actions_block_takes_precedence</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>test_mixed_actions_block_takes_precedence</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration:</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>test_orchestrator_blocks_harmful_output</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>test_orchestrator_blocks_harmful_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration:</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>test_orchestrator_warns_harmful_output</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>test_orchestrator_warns_harmful_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration:</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>test_orchestrator_replaces_harmful_output</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>test_orchestrator_replaces_harmful_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration:</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>test_orchestrator_no_filter</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>无过滤器</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration:</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>test_orchestrator_filter_disabled</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>过滤器禁用</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration:</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>test_orchestrator_clean_output</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>test_orchestrator_clean_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration:</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>test_orchestrator_filter_after_output_guard</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>test_orchestrator_filter_after_output_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentMiddleware:</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>test_middleware_replaces_output</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>test_middleware_replaces_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentMiddleware:</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>test_middleware_no_filter</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>中间件无过滤器</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentMiddleware:</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>test_middleware_filter_disabled</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>test_middleware_filter_disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentMiddleware:</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>test_middleware_no_harmful_data</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>test_middleware_no_harmful_data</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentMiddleware:</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>test_middleware_failed_result_skipped</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>test_middleware_failed_result_skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>TestHarmfulContentMiddleware:</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>test_middleware_priority</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>test_middleware_priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>TestCustomPatterns:</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>test_custom_pattern_matches</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>test_custom_pattern_matches</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>TestCustomPatterns:</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>test_custom_pattern_blocked</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>test_custom_pattern_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>TestCustomPatterns:</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>test_invalid_custom_pattern_ignored</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>test_invalid_custom_pattern_ignored</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>TestCustomPatterns:</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>test_custom_pattern_category_action</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>test_custom_pattern_category_action</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>TestEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>test_empty_input</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>空输入</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>TestEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>test_no_harmful_data</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>test_no_harmful_data</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>TestEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>test_multiple_categories_in_same_output</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>test_multiple_categories_in_same_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>TestEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>test_filter_disabled</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>test_filter_disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>TestEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>test_scan_tool_output</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>test_scan_tool_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>TestEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>test_scan_tool_output_no_harmful</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>test_scan_tool_output_no_harmful</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>TestEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>test_unicode_output</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>test_unicode_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>TestEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>test_very_long_output</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>超长输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>TestSummarizeHarmfulMatches:</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>test_empty_matches</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>test_empty_matches</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>TestSummarizeHarmfulMatches:</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>test_single_category</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>test_single_category</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>harmful_filter</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>TestSummarizeHarmfulMatches:</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>test_multiple_categories</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>多类别匹配</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1077"/>
+  <dimension ref="A1:E1134"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26737,6 +26737,1260 @@
         </is>
       </c>
     </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>TestValidationCheck:</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>test_creation</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>ValidationCheck 创建与默认 severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>TestValidationCheck:</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>test_severity_override</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>ValidationCheck severity 覆盖默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>TestValidationResult:</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>test_no_checks</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>ValidationResult 无检查项时不阻塞</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>TestValidationResult:</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>test_with_failed_checks</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>ValidationResult 含失败检查项</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>TestSummarizeValidationChecks:</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>test_empty</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>空检查列表摘要为空字符串</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>TestSummarizeValidationChecks:</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>test_single_type</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>单类型检查摘要格式</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>TestSummarizeValidationChecks:</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>test_multiple_types</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>多类型检查摘要格式含计数</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>TestResultValidatorBasics:</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>test_disabled_by_default</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>ResultValidatorConfig 默认禁用</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>TestResultValidatorBasics:</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>test_enabled_property</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>启用后 enabled 属性为 True</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>TestResultValidatorBasics:</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>test_disabled_validator_returns_unchanged</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>禁用状态下验证器不修改输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>TestResultValidatorBasics:</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>test_scan_tool_output_returns_unchanged</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>scan_tool_output 原样返回工具输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>TestFileExistsCheck:</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>test_file_exists_pass</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>文件存在时检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>TestFileExistsCheck:</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>test_file_not_exists_fail</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>文件不存在时检查失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>TestFileExistsCheck:</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>test_no_file_claims_no_checks</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>无文件声明时不生成文件检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>TestFileExistsCheck:</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>test_url_paths_ignored</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>URL 路径不被当作文件路径检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>TestFileExistsCheck:</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>test_file_claim_pattern_wrote</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>wrote file 模式被检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>TestFileExistsCheck:</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>test_file_claim_pattern_saved_to</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>saved to 模式被检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>TestFileExistsCheck:</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>test_file_claim_pattern_written_to</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>written to 模式被检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>TestFileExistsCheck:</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>test_duplicate_paths_deduplicated</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>重复路径只生成一次检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>TestFileExistsCheck:</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>test_file_exists_check_disabled</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>file_exists 检查禁用时不生成文件检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>TestCodeSyntaxCheck:</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>test_valid_python_code_passes</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>有效 Python 代码检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>TestCodeSyntaxCheck:</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>test_invalid_python_code_fails</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>无效 Python 代码检查失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>TestCodeSyntaxCheck:</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>test_no_correctness_claim_no_check</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>无正确性声明时不检查代码语法</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>TestCodeSyntaxCheck:</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>test_valid_json_passes</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>有效 JSON 检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>TestCodeSyntaxCheck:</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>test_invalid_json_fails</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>无效 JSON 检查失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>TestCodeSyntaxCheck:</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>test_code_syntax_check_disabled</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>code_syntax 检查禁用时不生成代码检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>TestCodeSyntaxCheck:</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>test_syntax_error_detail_contains_line</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>语法错误详情包含行号信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>TestCodeSyntaxCheck:</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>test_empty_code_block_ignored</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>空代码块不生成检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>TestCommandSuccessCheck:</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>test_claim_with_zero_exit_code_passes</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>退出码为 0 时命令成功检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>TestCommandSuccessCheck:</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>test_claim_with_nonzero_exit_code_fails</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>退出码非 0 时命令成功检查失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>TestCommandSuccessCheck:</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>test_no_command_claim_no_check</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>无命令成功声明时不检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>TestCommandSuccessCheck:</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>test_command_success_check_disabled</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>command_success 检查禁用时不生成命令检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>TestCommandSuccessCheck:</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>test_multiple_nonzero_exit_codes</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>多个非零退出码均被报告</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>TestOnFailActions:</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>test_annotate_appends_note</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>on_fail=annotate 追加验证备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>TestOnFailActions:</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>test_warn_appends_warning</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>on_fail=warn 追加验证警告</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>TestOnFailActions:</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>test_block_with_high_severity</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>on_fail=block 高严重度失败时阻塞输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>TestOnFailActions:</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>test_block_without_high_severity_does_not_block</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>on_fail=block 无高严重度失败时不阻塞</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>TestOnFailActions:</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>test_annotate_is_default</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>默认 on_fail 动作为 annotate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>TestOnPassActions:</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>test_silent_is_default</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>默认 on_pass 动作为 silent</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>TestOnPassActions:</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>test_silent_no_annotation</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>on_pass=silent 全部通过时不修改响应</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>TestOnPassActions:</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>test_annotate_appends_pass_note</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>on_pass=annotate 追加通过验证备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>TestNoChecksScenario:</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>test_no_claims_no_checks</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>无可验证声明时不生成检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>TestNoChecksScenario:</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>test_all_checks_pass_no_failure</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>全部检查通过时 failed_checks 为空</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>TestCustomValidators:</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>test_custom_validator_pass</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>自定义验证器通过时添加通过检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>TestCustomValidators:</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>test_custom_validator_fail</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>自定义验证器失败时添加失败检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>TestCustomValidators:</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>test_custom_validator_exception_handled</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>自定义验证器异常不影响验证流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>TestCustomValidators:</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>test_custom_validator_returns_none_skipped</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>自定义验证器返回 None 时跳过</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>TestEventEmission:</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>test_blocked_emits_validation_failed_event</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>阻塞时发出 VALIDATION_FAILED 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>TestEventEmission:</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>test_blocked_emits_output_blocked_event</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>阻塞时发出 OUTPUT_BLOCKED 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>TestEventEmission:</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>test_no_events_when_not_blocked</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>不阻塞时不发出 OUTPUT_BLOCKED 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration:</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>test_validator_result_stored</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>验证器结果存储为 last_validator_result</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>TestOrchestratorIntegration:</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>test_validator_not_set_when_none</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>验证器为 None 时 last_validator_result 保持 None</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>TestPatternEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>test_short_path_ignored</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>短路径被忽略不生成文件检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>TestPatternEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>test_data_url_ignored</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>data: URL 不被当作文件路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>TestPatternEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>test_chinese_file_claim</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>中文文件声明可正常检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>TestPatternEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>test_code_claim_with_function</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>含 function 关键词的代码正确性声明可检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>TestPatternEdgeCases:</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>test_command_claim_with_execution</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>命令执行声明可被检测</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1134"/>
+  <dimension ref="A1:E1162"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27991,6 +27991,622 @@
         </is>
       </c>
     </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>test_valid_status_schema_passes</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>STATUS 格式完整数据通过 schema 验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>test_status_missing_required_key</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>STATUS 缺少 status 必需键被检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>test_status_wrong_type</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>STATUS exit_code 类型错误被检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>test_status_python_executor_variant</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>STATUS 使用 output 键（PythonExecutor 变体）通过验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>test_list_schema_valid</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>LIST 格式完整数据通过 schema 验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>test_list_missing_items</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>LIST 缺少 items 必需键被检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>test_list_wrong_type_total</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>LIST total 类型错误被检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>test_content_schema_valid</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>CONTENT 格式完整数据通过 schema 验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>test_content_missing_source</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>CONTENT 缺少 source 必需键被检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>test_content_missing_content</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>CONTENT 缺少 content 必需键被检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>test_structure_always_passes</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>STRUCTURE 格式总是通过验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>test_error_schema_always_passes</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>ERROR 格式含可选键时通过验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>test_error_schema_empty_data_passes</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>ERROR 格式空数据通过验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>test_validate_tool_output_valid</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>validate_tool_output() 有效输入返回 (True, [])</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>test_validate_tool_output_invalid</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>validate_tool_output() 无效输入返回 (False, errors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>test_validate_tool_output_disabled_when_schema_not_in_checks</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>schema 不在 checks 列表时 validate_tool_output() 跳过</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>test_schema_check_not_in_validate_dispatch</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>schema 不通过 validate() 文本路径分发</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>test_validate_tool_output_emits_event</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>schema 失败时发射 VALIDATION_FAILED 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>TestSchemaValidation:</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>test_bool_value_rejected_for_int_key</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>bool 值被 int 类型检查拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>TestIsTypeCompatible:</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>test_str_matches_str</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>str 匹配 str 类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>TestIsTypeCompatible:</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>test_int_matches_int</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>int 匹配 int 类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>TestIsTypeCompatible:</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>test_bool_rejected_for_int</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>bool 被拒绝匹配 int 类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>TestIsTypeCompatible:</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>test_bool_accepted_for_bool</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>bool 匹配 bool 类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>TestIsTypeCompatible:</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>test_int_accepted_for_float</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>int 被接受匹配 float 类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>TestIsTypeCompatible:</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>test_str_rejected_for_int</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>str 被拒绝匹配 int 类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>TestIsTypeCompatible:</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>test_list_matches_list</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>list 匹配 list 类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>TestFormatSchema:</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>test_format_schemas_use_dataclass</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>FORMAT_SCHEMAS 值均为 FormatSchema 实例</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>result_validator</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>TestFormatSchema:</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>test_required_keys_are_tuple</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>所有 schema 的 required_keys 为 tuple 类型</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1162"/>
+  <dimension ref="A1:E1191"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28607,6 +28607,644 @@
         </is>
       </c>
     </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>TestFeedbackLoopConfig</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>test_default_config</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>FeedbackLoopConfig 默认配置值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>TestFeedbackLoopConfig</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>test_custom_config</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>FeedbackLoopConfig 自定义配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>test_disabled_no_injection</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>偏差反馈禁用时不注入</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>test_no_warning_no_injection</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>无警告时不注入</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>test_warning_with_cooldown_first_injection</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>首次警告触发注入 (cooldown=3, 1%3==1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>test_warning_with_cooldown_second_no_injection</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>第二次警告不注入 (2%3!=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>test_warning_with_cooldown_third_no_injection</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>第三次警告不注入 (3%3!=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>test_warning_with_cooldown_fourth_injection</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>第四次警告触发注入 (4%3==1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>test_over_estimation_hint</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>高估偏差提示包含'高估'或'低于估算'</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>test_under_estimation_hint</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>低估偏差提示包含'低估'或'远超估算'</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>test_hint_injection_disabled</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>hint_injection=False 时 should_inject=True 但 hint=None</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>test_hint_cycles_through_templates</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>提示模板循环使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>test_deviation_pct_in_result</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>结果包含正确的偏差百分比</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>test_event_emission</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>偏差反馈注入时发射事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>test_no_event_when_not_injecting</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>不注入时不发射事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>TestDeviationFeedback</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>test_deviation_injections_counter</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>注入计数器追踪</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>TestSelfCorrection</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>test_disabled_no_retry</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>自纠正禁用时不重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>TestSelfCorrection</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>test_blocked_with_attempts_remaining</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>blocked 且有余量时重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>TestSelfCorrection</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>test_all_attempts_exhausted</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>尝试耗尽后不重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>TestSelfCorrection</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>test_non_blocked_no_retry</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>非 blocked 不重试</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>TestSelfCorrection</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>test_feedback_message_format</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>反馈消息格式正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>TestSelfCorrection</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>test_correction_attempt_tracking</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>纠正尝试计数追踪</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>TestSelfCorrection</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>test_remaining_attempts_never_negative</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>剩余尝试次数不为负</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>TestSelfCorrection</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>test_event_emission</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>自纠正事件发射</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>TestSelfCorrection</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>test_termination_reason_exhausted</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>终止原因为 SELF_CORRECTION_EXHAUSTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>TestFeedbackLoopReset</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>test_reset_all_clears_all_state</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>reset_all() 清除所有状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>TestFeedbackLoopReset</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>test_reset_run_preserves_correction_state</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>reset_run() 保留纠正状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>TestFeedbackLoopReset</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>test_reset_all_clears_hint_indices</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>reset_all() 清除提示索引</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>feedback_loop</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>TestSelfCorrectionResult</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>test_result_fields</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>SelfCorrectionResult 字段验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1191"/>
+  <dimension ref="A1:E1231"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29245,6 +29245,886 @@
         </is>
       </c>
     </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>TestMiniTokenBucket</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>test_initial_tokens_equal_max</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>初始令牌数等于最大值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>TestMiniTokenBucket</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>test_try_acquire_success</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>初始获取令牌成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>TestMiniTokenBucket</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>test_try_acquire_decrements</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>获取令牌递减直到耗尽</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>TestMiniTokenBucket</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>test_refill_over_time</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>令牌随时间恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>TestMiniTokenBucket</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>test_wait_time_zero_when_tokens_available</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>有令牌时等待时间为0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>TestMiniTokenBucket</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>test_wait_time_positive_when_empty</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>令牌耗尽时等待时间&gt;0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>TestMiniTokenBucket</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>test_reset_restores_full_capacity</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>reset恢复满容量</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>TestMiniTokenBucket</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>test_tokens_capped_at_max</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>令牌数不超过最大值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>TestMiniTokenBucket</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>test_release_returns_token</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>release归还令牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>TestMiniTokenBucket</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>test_release_capped_at_max</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>release不超过最大值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>TestToolTimeoutWrapper</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>test_get_timeout_default</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>获取默认超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>TestToolTimeoutWrapper</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>test_get_timeout_override</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>获取覆盖超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>TestToolTimeoutWrapper</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>test_get_timeout_zero_means_no_timeout</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>超时为0表示不限时</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>TestToolTimeoutWrapper</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>test_execute_with_timeout_fast_function</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>快速函数正常执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>TestToolTimeoutWrapper</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>test_execute_with_timeout_no_timeout_when_zero</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>超时为0直接执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>TestToolTimeoutWrapper</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>test_should_wrap_tool_without_builtin_timeout</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>无内置超时工具应包装</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>TestToolTimeoutWrapper</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>test_should_skip_tool_with_builtin_timeout</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>有内置超时工具跳过包装</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>TestToolTimeoutWrapper</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>test_execute_with_timeout_handles_exception</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>执行异常正确处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>TestToolRateLimiter</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>test_first_call_allowed</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>首次调用允许</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>TestToolRateLimiter</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>test_per_tool_rate_limit</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>单工具频率限制</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>TestToolRateLimiter</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>test_global_rate_limit</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>全局频率限制</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>TestToolRateLimiter</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>test_different_tools_have_separate_buckets</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>不同工具独立令牌桶</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>TestToolRateLimiter</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>test_rate_limit_result_has_wait_time</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>限流结果包含等待时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>TestToolRateLimiter</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>test_rate_limit_result_has_calls_remaining</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>限流结果包含剩余次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>TestToolRateLimiter</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>test_reset_clears_all_limits</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>reset清除所有限制</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>TestToolRateLimiter</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>test_global_token_returned_on_per_tool_rejection</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>per-tool拒绝时归还global token</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>TestToolResourceLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>test_defaults</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>配置默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>TestToolResourceLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>test_custom_values</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>自定义配置值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>TestToolResourceLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>test_validation_negative_timeout</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>验证负超时拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>TestToolResourceLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>test_validation_negative_per_tool</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>验证零per_tool拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>TestToolResourceLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>test_validation_negative_global</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>验证负global拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>TestToolResourceLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>test_timeout_overrides_default_empty</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>timeout_overrides默认为空</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>TestToolResourceLimiterConfig</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>test_timeout_overrides_custom</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>自定义timeout_overrides</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>TestSubsystemsIntegration</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>test_subsystems_creates_timeout_wrapper</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>子系统创建timeout_wrapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>TestSubsystemsIntegration</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>test_subsystems_creates_rate_limiter</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>子系统创建rate_limiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>TestSubsystemsIntegration</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>test_subsystems_creates_both</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>子系统同时创建两者</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>TestSubsystemsIntegration</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>test_subsystems_disabled_creates_neither</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>禁用时不创建</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>TestSubsystemsIntegration</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>test_subsystems_none_config_creates_neither</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>None配置不创建</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>TestBaseToolBuiltinTimeout</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>test_default_is_false</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>默认has_builtin_timeout=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>resource_limiter</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>TestBaseToolBuiltinTimeout</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>test_can_set_to_true</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>可设置has_builtin_timeout=True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1231"/>
+  <dimension ref="A1:E1258"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30125,6 +30125,600 @@
         </is>
       </c>
     </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>TestLongTermEntryCompat</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>test_from_dict_defaults_mention_count</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>from_dict 缺失 mention_count 默认为 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>TestLongTermEntryCompat</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>test_from_dict_defaults_last_mentioned_at</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>from_dict 缺失 last_mentioned_at 默认为 created_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>TestLongTermEntryCompat</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>test_from_dict_preserves_mention_count</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>from_dict 保留显式 mention_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>TestLongTermEntryCompat</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>test_from_dict_preserves_last_mentioned_at</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>from_dict 保留显式 last_mentioned_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>TestDecayWeight</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>test_fresh_entry_full_weight</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>新条目衰减权重 = importance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>TestDecayWeight</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>test_half_life_entry</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>半衰期时权重 = importance/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>TestDecayWeight</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>test_old_entry_near_zero</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>旧条目权重趋近 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>TestDecayWeight</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>test_uses_last_mentioned_at</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>衰减基于 last_mentioned_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>TestDecayWeight</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>test_fallback_to_created_at</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>无 last_mentioned_at 时用 created_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>TestDecayWeight</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>test_zero_importance</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>importance=0 时权重为 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>TestEnhancedDedup</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>test_new_entry_created</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>无相似条目时创建新条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>TestEnhancedDedup</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>test_similar_entry_mention_count_incremented</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>相似条目 mention_count 递增</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>TestEnhancedDedup</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>test_similar_entry_last_mentioned_at_updated</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>相似条目 last_mentioned_at 更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>TestEnhancedDedup</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>test_similar_entry_keywords_merged</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>相似条目关键词取并集</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>TestEnhancedDedup</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>test_similar_entry_importance_max</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>相似条目 importance 取 max</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>TestEnhancedDedup</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>test_similar_entry_metadata_merged</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>相似条目 metadata 新覆盖旧</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>TestEnhancedDedup</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>test_same_meta_type_replaces_content</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>同 metadata.type 时替换内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>TestSearchWithDecay</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>test_search_without_decay</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>无衰减时按 importance 排序</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>TestSearchWithDecay</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>test_search_with_decay_prefers_recent</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>衰减时优先返回近期条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>TestSearchWithDecay</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>test_search_mention_boost</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>mention_count 提升搜索排名</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>TestMemoryGC</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>test_gc_removes_low_weight_old_entries</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>GC 清理低权重旧条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>TestMemoryGC</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>test_gc_keeps_recent_entries</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>GC 保留近期条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>TestMemoryGC</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>test_gc_disabled</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>GC 禁用时不清理</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>TestHybridMemoryGC</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>test_set_memory_gc_config</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>设置 memory_gc 配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>TestHybridMemoryGC</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>test_memorize_uses_merge_tag</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>memorize 使用 merge_tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>TestHybridMemoryGC</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>test_recall_uses_decay</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>recall 启用衰减排序</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>TestHybridMemoryGC</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>test_run_gc</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>HybridMemory 委托 GC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1258"/>
+  <dimension ref="A1:E1271"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30719,6 +30719,292 @@
         </is>
       </c>
     </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>TestGCResultEvictionFields</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>test_default_eviction_fields</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>GCResult 淘汰字段默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>TestGCResultEvictionFields</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>test_eviction_fields_populated</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>GCResult 淘汰字段赋值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>TestMemoryGCEviction</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>test_eviction_disabled_no_removal</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>淘汰禁用时不清理</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>TestMemoryGCEviction</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>test_eviction_no_op_when_below_capacity</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>低于容量上限不淘汰</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>TestMemoryGCEviction</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>test_eviction_removes_lowest_weight</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>淘汰最低权重条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>TestMemoryGCEviction</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>test_eviction_protected_category_not_removed</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>保护类别不被淘汰</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>TestMemoryGCEviction</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>test_eviction_mention_count_protection</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>提及次数达标不被淘汰</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>TestMemoryGCEviction</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>test_eviction_respects_max_entries</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>淘汰数量精确到容量上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>TestMemoryGCEviction</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>test_eviction_after_decay_cleanup</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>衰减清理后再判断淘汰</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>TestMemoryGCEviction</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>test_eviction_tiebreak_by_age</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>同权重时老条目优先淘汰</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>TestMemoryGCEviction</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>test_eviction_combined_with_decay</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>衰减+淘汰联合清理</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>TestHybridMemoryEviction</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>test_run_gc_returns_eviction_stats</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>run_gc 返回淘汰统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>memory_gc</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>TestHybridMemoryEviction</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>test_eviction_config_propagates</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>淘汰配置传播到 HybridMemory</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1271"/>
+  <dimension ref="A1:E1299"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31005,6 +31005,622 @@
         </is>
       </c>
     </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>TestSnapshotMetadata</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>test_to_dict_from_dict_roundtrip</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>to_dict/from_dict 往返一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>TestSnapshotMetadata</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>test_from_dict_missing_optional_fields</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>缺失可选字段时使用默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>TestSnapshot</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>test_to_dict_from_dict_roundtrip</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>to_dict/from_dict 往返一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>TestSnapshot</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>test_from_dict_extra_fields_ignored</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>多余字段被忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerSave</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>test_save_creates_json_file</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>save 创建 JSON 文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerSave</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>test_save_returns_metadata</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>save 返回 SnapshotMetadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerSave</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>test_save_with_empty_name</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>save 空名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerSave</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>test_save_emits_event</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>save 触发 SNAPSHOT_SAVED 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerSave</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>test_save_captures_all_sections</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>save 捕获所有状态段</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerSave</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>test_save_enforces_max_snapshots</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>save 超过上限时淘汰最旧</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerRestore</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>test_restore_replaces_agent_fields</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>restore 替换 agent 字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerRestore</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>test_restore_replaces_orchestrator_fields</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>restore 替换 orchestrator 字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerRestore</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>test_restore_emits_event</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>restore 触发 SNAPSHOT_RESTORED 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerRestore</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>test_restore_nonexistent_returns_false</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>restore 不存在快照返回 False</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerRestore</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>test_restore_memory_messages_correct</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>restore 恢复正确的消息列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerRestore</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>test_restore_calls_setup_system_prompt</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>restore 后调用 _setup_system_prompt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerList</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>test_list_empty</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>list 空目录返回空列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerList</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>test_list_returns_metadata</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>list 返回 SnapshotMetadata 列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerList</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>test_list_sorted_by_creation_time</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>list 按创建时间降序排列</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerDelete</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>test_delete_removes_file</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>delete 删除文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerDelete</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>test_delete_nonexistent_returns_false</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>delete 不存在快照返回 False</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>TestSnapshotRoundtrip</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>test_save_restore_roundtrip</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>完整保存/恢复往返一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>TestSnapshotRoundtrip</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>test_save_restore_token_budget</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>token_budget 保存/恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>TestSnapshotRoundtrip</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>test_save_restore_circuit_breaker</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>circuit_breaker 保存/恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>TestAutoSnapshot</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>test_auto_snapshot_disabled_by_default</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>auto_snapshot 默认关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>TestAutoSnapshot</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>test_auto_snapshot_before_run</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>auto_snapshot 在 run 前自动保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>TestSnapshotConfig</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>test_snapshot_config_defaults</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>SnapshotConfig 默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>TestSnapshotConfig</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>test_snapshot_config_in_main_config</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>SnapshotConfig 在 Config 中存在</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1299"/>
+  <dimension ref="A1:E1334"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31621,6 +31621,776 @@
         </is>
       </c>
     </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureConfig</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>test_defaults</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>ConsecutiveFailureConfig 默认值 (enabled=True, threshold=3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureConfig</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>test_custom_values</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>自定义配置值 (enabled=False, threshold=5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorRecordAndReset</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>test_success_resets_counter</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>成功重置失败计数器为 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorRecordAndReset</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>test_failure_increments_counter</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>失败递增计数器并记录最后工具/错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorRecordAndReset</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>test_reset_clears_state</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>reset() 清除所有跟踪状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorCheck</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>test_not_triggered_below_threshold</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>低于阈值返回 triggered=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorCheck</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>test_triggered_at_threshold</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>达到阈值返回 triggered=True 含详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorCheck</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>test_triggered_above_threshold</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>超过阈值仍然触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorCheck</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>test_success_resets_then_failure_recount</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>成功重置后新失败从 0 重新计数</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorCheck</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>test_disabled_never_triggers</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>禁用配置永不触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorCheck</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>test_default_config_threshold_3</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>默认阈值为 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorState</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>test_get_set_state_roundtrip</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>get_state/set_state 保持所有字段一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorState</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>test_set_state_default_values</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>set_state({}) 使用默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>consecutive_failure</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>TestConsecutiveFailureDetectorState</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>test_state_after_reset</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>重置后状态归零</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>TestAuditLogEntry</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>test_to_dict_from_dict_roundtrip</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>AuditLogEntry 序列化往返一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>TestAuditLogEntry</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>test_from_dict_missing_optional_fields</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>缺失字段使用默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAudit</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>test_save_records_audit</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>save 操作记录审计条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAudit</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>test_restore_records_audit</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>restore 操作记录审计条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAudit</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>test_delete_records_audit</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>delete 操作记录审计条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAudit</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>test_audit_log_disabled</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>禁用审计时不写入文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAudit</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>test_list_audit_entries_sorted_by_time</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>审计条目按时间降序排列</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAudit</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>test_list_audit_entries_empty</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>空日志返回 []</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAudit</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>test_save_emits_audit_event</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>save 触发 AUDIT_LOG_ENTRY 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAudit</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>test_delete_emits_snapshot_deleted_event</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>delete 触发 SNAPSHOT_DELETED 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerRollbackFromAudit</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>test_rollback_from_save_audit</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>从 save 审计条目回滚</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerRollbackFromAudit</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>test_rollback_from_nonexistent_audit</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>不存在的 audit_id 返回 False</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerRollbackFromAudit</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>test_rollback_from_delete_audit_fails</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>不能从 delete 条目回滚</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAutoRollback</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>test_auto_rollback_restores_latest_snapshot</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>自动回滚恢复最新快照</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAutoRollback</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>test_auto_rollback_no_snapshots</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>无快照时返回 False</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAutoRollback</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>test_auto_rollback_disabled</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>禁用时返回 False</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAutoRollback</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>test_auto_rollback_emits_events</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>自动回滚触发 AUTO_ROLLBACK_COMPLETED 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>TestSnapshotManagerAutoRollback</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>test_auto_rollback_records_audit</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>自动回滚记录审计条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>TestSnapshotWithConsecutiveFailure</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>test_snapshot_captures_cfd_state</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>快照 JSON 捕获 CFD 状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>TestSnapshotWithConsecutiveFailure</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>test_restore_applies_cfd_state</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>从快照恢复 CFD 状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>TestSnapshotWithConsecutiveFailure</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>test_from_dict_backward_compat_no_cfd</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>v0.8.14 快照加载时 CFD 使用默认值</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1334"/>
+  <dimension ref="A1:E1350"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32391,6 +32391,358 @@
         </is>
       </c>
     </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>TestExecutionEventType</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>test_all_event_types_defined</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>ExecutionEventType 枚举包含全部 9 种事件类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>TestExecutionEventType</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>test_event_type_values</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>ExecutionEventType 枚举值与字符串匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>TestExecutionEvent</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>test_default_fields_are_none</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>ExecutionEvent 默认 typed 字段为 None</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>TestExecutionEvent</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>test_typed_fields_populated</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>ExecutionEvent typed 字段正确填充</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>TestExecutionHandle</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>test_handle_wraps_generator</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>ExecutionHandle 包装 generator 并可迭代</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>TestExecutionHandle</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>test_cancel_sets_flag</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>ExecutionHandle.cancel() 设置 cancelled 标志</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>TestThinkStream</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>test_yields_think_events</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>_think_stream() yield THINK_START/TEXT/END 并返回 ThinkResult</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>TestThinkStream</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>test_think_wrapper_returns_same_result</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>_think() 与 _think_stream() 返回相同 ThinkResult</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>TestRunStream</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>test_simple_final_answer</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>run_stream() 简单最终答案事件序列</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>TestRunStream</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>test_one_tool_call_round</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>run_stream() 一轮工具调用事件序列</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>TestRunStream</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>test_guard_short_circuit</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>run_stream() guard 短路 yield GUARD_SHORT_CIRCUIT + RUN_END</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>TestRunStream</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>test_cancellation</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>run_stream() 取消 yield CANCELLED + RUN_END</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>TestRunStream</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>test_run_and_run_stream_equivalent</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>run() 与 run_stream() 最终结果相同</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>TestOrchestratorRunStream</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>test_basic_orchestrator_stream</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Orchestrator run_stream() 基本事件序列</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>TestOrchestratorRunStream</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>test_run_and_run_stream_equivalent</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Orchestrator run() 与 run_stream() 结果等价</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>TestOrchestratorRunStream</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>test_sanitizer_rejection_yields_run_end</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Sanitizer 拒绝 yield RUN_END + INPUT_REJECTED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1350"/>
+  <dimension ref="A1:E1373"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32743,6 +32743,512 @@
         </is>
       </c>
     </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>TestStreamChunk</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>test_default_values</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>StreamChunk 默认值验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>TestStreamChunk</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>test_text_chunk</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>StreamChunk 文本块</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>TestStreamChunk</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>test_tool_call_chunk</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>StreamChunk 工具调用块</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>TestStreamChunk</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>test_usage_chunk</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>StreamChunk 用量块</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>TestAsyncExecutionHandle</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>test_collect_result</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>AsyncExecutionHandle 收集结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>TestAsyncExecutionHandle</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>test_cancel</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>AsyncExecutionHandle 取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>TestAsyncExecutionHandle</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>test_collect_result_no_run_end</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>AsyncExecutionHandle 无 RUN_END 返回 None</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>TestBaseLLMAsyncInterface</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>test_ollama_has_async_impl</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>OllamaLLM 实现 _chat_stream_async_impl</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>TestBaseLLMAsyncInterface</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>test_openai_compatible_has_async_impl</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>OpenAICompatibleLLM 实现 _chat_stream_async_impl</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>TestBaseLLMAsyncInterface</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>test_anthropic_has_async_impl</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>AnthropicLLM 实现 _chat_stream_async_impl</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>TestOllamaLLMAsyncStream</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>test_text_streaming</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>OllamaLLM 异步文本流</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>TestOllamaLLMAsyncStream</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>test_tool_call_streaming</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>OllamaLLM 异步工具调用流</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>TestOpenAICompatibleLLMAsyncStream</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>test_text_streaming</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>OpenAICompatibleLLM 异步文本流</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>TestOpenAICompatibleLLMAsyncStream</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>test_tool_call_incremental</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>OpenAICompatibleLLM 增量工具调用缓冲</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>TestAnthropicLLMAsyncStream</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>test_text_streaming</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>AnthropicLLM 异步文本流</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>TestAnthropicLLMAsyncStream</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>test_tool_call_streaming</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>AnthropicLLM 异步工具调用流</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>TestThinkStreamAsync</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>test_token_by_token_think_text</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>逐 token THINK_TEXT 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>TestRunStreamAsyncSimpleAnswer</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>test_simple_answer</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>异步流式简单答案</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>TestRunStreamAsyncCancellation</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>test_cancel_during_execution</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>异步流式取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>TestSyncAsyncParity</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>test_same_final_result</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>同步/异步路径结果等价</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>TestStreamingConfig</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>test_default_mode</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>StreamingConfig 默认 mode=sync</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>TestStreamingConfig</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>test_async_mode</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>StreamingConfig mode=async</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>async_streaming</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>TestStreamingConfig</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>test_config_has_streaming</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>Config 包含 streaming 字段</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1373"/>
+  <dimension ref="A1:E1374"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33249,6 +33249,33 @@
         </is>
       </c>
     </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>TestBaseRatioFirstRoundCorrection</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>test_get_base_chars_before_start_run</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>MetricsTracker 在未调用 start_run() 时 get_base_chars() 也能正常返回零值字典</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>AttributeError（__init__ 遗漏属性初始化）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1374"/>
+  <dimension ref="A1:E1376"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33276,6 +33276,60 @@
         </is>
       </c>
     </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>TestPersistentMemory</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>test_ephemeral_message_not_persisted</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Ephemeral 标记的消息跳过 storage.save()，重新加载后不在上下文中</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>AttributeError / 跨轮次残留（BUG-007）</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>TestPersistentMemory</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>test_load_filters_old_system_messages</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>加载旧会话时过滤 [System] 前缀的 user 消息，保留正常消息</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>LLM 幻觉 / 旧 [System] 残留误导</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1376"/>
+  <dimension ref="A1:E1379"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33330,6 +33330,87 @@
         </is>
       </c>
     </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>TestStallDetectorSimilarity</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>test_same_tool_same_size_stall</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>同工具+同规模+同成功状态应判定停滞（BUG-006 核心修复）</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>StallDetector 相似度恒为 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>TestStallDetectorSimilarity</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>test_different_size_no_stall</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>不同结果量级不应判定停滞</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>StallDetector 误判</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>TestStallDetectorSimilarity</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>test_fail_vs_success_no_stall</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>失败结果与成功结果不应判定停滞</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>StallDetector 误判</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1379"/>
+  <dimension ref="A1:E1380"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33411,6 +33411,33 @@
         </is>
       </c>
     </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>TestStallDetectorSimilarity</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>test_fractional_jaccard_similarity</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>部分重叠签名应产生 (0,1) 之间的 Jaccard 相似度</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>BUG-006 回归：Jaccard 恒为 0/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1380"/>
+  <dimension ref="A1:E1381"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33438,6 +33438,33 @@
         </is>
       </c>
     </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>TestPersistentMemory</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>test_load_filters_stale_system_prompt</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>加载旧会话时过滤 role==system 的残留 system prompt，确保由 _setup_system_prompt() 重新生成</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>旧的空 tools 列表 system prompt 残留导致 LLM 不调用工具</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1381"/>
+  <dimension ref="A1:E1382"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33465,6 +33465,33 @@
         </is>
       </c>
     </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>TestAgentOrchestrator</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>test_orchestrator_and_agent_events_are_separate</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>验证 orchestrator.events 和 agent.events 是独立的 EventEmitter，事件不转发</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>async 路径确认 handler 收不到事件导致工具永久阻塞</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1382"/>
+  <dimension ref="A1:E1387"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33492,6 +33492,129 @@
         </is>
       </c>
     </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>TestMessageNormalizer</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>test_openai_normalizer_noop</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>OpenAI normalizer 不修改消息</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr"/>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>TestMessageNormalizer</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>test_deepseek_normalizer_adds_reasoning_content</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>DeepSeek normalizer 补全空 reasoning_content</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>DeepSeek API 400 错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>TestMessageNormalizer</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>test_deepseek_normalizer_skips_if_present</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>已有的 reasoning_content 不被覆盖</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr"/>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>TestMessageNormalizer</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>test_xfyun_normalizer_skips_empty_id</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>讯飞空 id/name 不覆盖已有值</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>讯飞 SSE delta 覆盖 tool_call name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>TestMessageNormalizer</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>test_select_normalizer_by_model</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>模型名匹配到正确的 Normalizer</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1387"/>
+  <dimension ref="A1:E1397"/>
   <sheetFormatPr baseColWidth="15" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33513,7 +33513,6 @@
           <t>OpenAI normalizer 不修改消息</t>
         </is>
       </c>
-      <c r="E1383" t="inlineStr"/>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
@@ -33563,7 +33562,6 @@
           <t>已有的 reasoning_content 不被覆盖</t>
         </is>
       </c>
-      <c r="E1385" t="inlineStr"/>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
@@ -33613,7 +33611,276 @@
           <t>模型名匹配到正确的 Normalizer</t>
         </is>
       </c>
-      <c r="E1387" t="inlineStr"/>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>TestVerbosityLevels</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>test_quiet_only_tui_and_error</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>验证 quiet 仅 TUI+ERROR 可见</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>冗度过滤不生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>TestVerbosityLevels</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>test_minimal_adds_warning_and_lifecycle</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>验证 minimal + WARNING+LIFECYCLE</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>冗度过滤不生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>TestVerbosityLevels</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>test_verbose_shows_all</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>验证 verbose 全部可见</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>冗度过滤不生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>TestVerbosityLevels</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>test_module_overrides</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>验证模块级覆写仅覆盖指定模块</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>模块覆写不生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>TestVerbosityLevels</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>test_module_override_never_hides_error</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>验证模块覆写不能隐藏 ERROR</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>ERROR 被意外隐藏</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>TestParseVerbosity</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>test_english_names</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>验证英文冗度名解析</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>解析失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>TestParseVerbosity</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>test_chinese_and_numeric</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>验证中文/数字冗度名解析</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>解析失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>TestParseVerbosity</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>test_case_insensitive</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>验证大小写不敏感</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>解析失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>TestParseVerbosity</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>test_invalid_raises</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>验证无效值抛出 ValueError</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>未抛出异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>TestTUIAlwaysVisible</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>test_tui_methods_work_at_all_levels</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>验证 TUI 在所有冗度级别均可见</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>TUI 输出被过滤</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
